--- a/setup_files/article.xlsx
+++ b/setup_files/article.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/fskfe_dtu_dk/Documents/Dokumenter/DTU_Man/Speciale/setup_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="949" documentId="8_{3A720C2A-8BB2-46CC-9A31-194013BDD676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{085FA516-2EA2-4AA3-AAA4-C6A268E17639}"/>
+  <xr:revisionPtr revIDLastSave="1026" documentId="8_{3A720C2A-8BB2-46CC-9A31-194013BDD676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DCAB517-9AF6-4813-913C-F69EFF9D7A2A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{7643C590-AB87-4ECC-9949-F1DE609BD7D2}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7643C590-AB87-4ECC-9949-F1DE609BD7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="7" r:id="rId1"/>
@@ -361,7 +361,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="108">
   <si>
     <t>Electrolyzer</t>
   </si>
@@ -609,24 +609,9 @@
     <t>Changed Object</t>
   </si>
   <si>
-    <t>80percent_ammonia</t>
-  </si>
-  <si>
     <t>Scenario Name</t>
   </si>
   <si>
-    <t>70percent_ammonia</t>
-  </si>
-  <si>
-    <t>60percent_ammonia</t>
-  </si>
-  <si>
-    <t>50percent_ammonia</t>
-  </si>
-  <si>
-    <t>40percent_ammonia</t>
-  </si>
-  <si>
     <t>no_solar_power</t>
   </si>
   <si>
@@ -636,12 +621,6 @@
     <t>component</t>
   </si>
   <si>
-    <t>30percent_ammonia</t>
-  </si>
-  <si>
-    <t>20percent_ammonia</t>
-  </si>
-  <si>
     <t>base_case_no_spot</t>
   </si>
   <si>
@@ -700,6 +679,12 @@
   </si>
   <si>
     <t>reversible</t>
+  </si>
+  <si>
+    <t>flexible_contract</t>
+  </si>
+  <si>
+    <t>flexible_ammonia</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1156,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>78</v>
@@ -1187,8 +1172,8 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>82</v>
+      <c r="A2">
+        <v>110</v>
       </c>
       <c r="B2" t="s">
         <v>80</v>
@@ -1200,30 +1185,31 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <f>Components!C7*8760*0.8</f>
-        <v>175200</v>
+        <f>Contracts!E$3*A2/100</f>
+        <v>110000</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>82</v>
+      <c r="A3">
+        <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>30000</v>
+        <f>Contracts!E$3*A3/100</f>
+        <v>120000</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>84</v>
+      <c r="A4">
+        <v>130</v>
       </c>
       <c r="B4" t="s">
         <v>80</v>
@@ -1235,30 +1221,31 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <f>Components!C7*8760*0.7</f>
-        <v>153300</v>
+        <f>MIN(Contracts!E$3*A4/100,10680*12)</f>
+        <v>128160</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>84</v>
+      <c r="A5">
+        <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>30000</v>
+        <f>Contracts!E$3*A5/100</f>
+        <v>90000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>85</v>
+      <c r="A6">
+        <v>80</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
@@ -1270,13 +1257,13 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <f>Components!C7*8760*0.6</f>
-        <v>131400</v>
+        <f>Contracts!E$3*A6/100</f>
+        <v>80000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>86</v>
+      <c r="A7">
+        <v>70</v>
       </c>
       <c r="B7" t="s">
         <v>80</v>
@@ -1288,49 +1275,48 @@
         <v>21</v>
       </c>
       <c r="E7">
-        <f>Components!C7*8760*0.5</f>
-        <v>109500</v>
+        <f>Contracts!E$3*A7/100</f>
+        <v>70000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <f>Components!C7*8760*0.4</f>
-        <v>87600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <f>Components!C7*8760*0.3</f>
-        <v>65700</v>
+        <f>PPAs!C3*1.5</f>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
@@ -1342,13 +1328,13 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <f>Components!C7*8760*0.2</f>
-        <v>43800</v>
+        <f>Components!C$7*8760*0.3</f>
+        <v>65700</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
@@ -1360,12 +1346,13 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <f>PPAs!C2*1.5</f>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
@@ -1383,97 +1370,95 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <f>E12+E11+PPAs!C4</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
         <v>80</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>33</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>21</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <f>Components!C$7*8760*0.3</f>
         <v>65700</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14">
-        <f>PPAs!C2*1.5</f>
-        <v>450</v>
-      </c>
-    </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E15">
-        <f>PPAs!C3*1.5</f>
-        <v>300</v>
+        <f>Components!C$7*8760*0.3</f>
+        <v>65700</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="E16">
-        <f>E15+E14+PPAs!C4</f>
-        <v>800</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
         <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="E17">
-        <f>Components!C$7*8760*0.3</f>
-        <v>65700</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
         <v>80</v>
@@ -1482,11 +1467,10 @@
         <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="E18">
-        <f>Components!C$7*8760*0.3</f>
-        <v>65700</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1576,7 +1560,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>37</v>
@@ -1591,37 +1575,37 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>61</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>65</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>7</v>
@@ -1777,7 +1761,7 @@
         <v>22</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="N4" s="2">
         <v>0.15</v>
@@ -1943,7 +1927,7 @@
         <v>22</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="N7" s="2">
         <v>0.107</v>
@@ -2150,7 +2134,7 @@
         <v>45</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>48</v>
@@ -2303,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -2340,7 +2324,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>37</v>
@@ -2397,7 +2381,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2433,12 +2417,12 @@
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>69</v>
@@ -2454,7 +2438,7 @@
         <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>59</v>
@@ -2469,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
